--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff697d77a05
-	0x7ff697d77a60
-	0x7ff697af16ad
-	0x7ff697b4a13e
-	0x7ff697b4a44c
-	0x7ff697b9ebe7
-	0x7ff697b9b8fb
-	0x7ff697b3b068
-	0x7ff697b3be93
-	0x7ff6980329a0
-	0x7ff69802ce20
-	0x7ff69804cc15
-	0x7ff697d9309e
-	0x7ff697d9ad8f
-	0x7ff697d80be4
-	0x7ff697d80d9f
-	0x7ff697d667f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff697d77a05
-	0x7ff697d77a60
-	0x7ff697af16ad
-	0x7ff697b4a13e
-	0x7ff697b4a44c
-	0x7ff697b9ebe7
-	0x7ff697b9b8fb
-	0x7ff697b3b068
-	0x7ff697b3be93
-	0x7ff6980329a0
-	0x7ff69802ce20
-	0x7ff69804cc15
-	0x7ff697d9309e
-	0x7ff697d9ad8f
-	0x7ff697d80be4
-	0x7ff697d80d9f
-	0x7ff697d667f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff697d77a05
-	0x7ff697d77a60
-	0x7ff697af16ad
-	0x7ff697b4a13e
-	0x7ff697b4a44c
-	0x7ff697b9ebe7
-	0x7ff697b9b8fb
-	0x7ff697b3b068
-	0x7ff697b3be93
-	0x7ff6980329a0
-	0x7ff69802ce20
-	0x7ff69804cc15
-	0x7ff697d9309e
-	0x7ff697d9ad8f
-	0x7ff697d80be4
-	0x7ff697d80d9f
-	0x7ff697d667f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff697d77a05
-	0x7ff697d77a60
-	0x7ff697af16ad
-	0x7ff697b4a13e
-	0x7ff697b4a44c
-	0x7ff697b9ebe7
-	0x7ff697b9b8fb
-	0x7ff697b3b068
-	0x7ff697b3be93
-	0x7ff6980329a0
-	0x7ff69802ce20
-	0x7ff69804cc15
-	0x7ff697d9309e
-	0x7ff697d9ad8f
-	0x7ff697d80be4
-	0x7ff697d80d9f
-	0x7ff697d667f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£18.40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff697d77a05
-	0x7ff697d77a60
-	0x7ff697af16ad
-	0x7ff697b4a13e
-	0x7ff697b4a44c
-	0x7ff697b9ebe7
-	0x7ff697b9b8fb
-	0x7ff697b3b068
-	0x7ff697b3be93
-	0x7ff6980329a0
-	0x7ff69802ce20
-	0x7ff69804cc15
-	0x7ff697d9309e
-	0x7ff697d9ad8f
-	0x7ff697d80be4
-	0x7ff697d80d9f
-	0x7ff697d667f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6ded47a05
-	0x7ff6ded47a60
-	0x7ff6deac16ad
-	0x7ff6deb1a13e
-	0x7ff6deb1a44c
-	0x7ff6deb6ebe7
-	0x7ff6deb6b8fb
-	0x7ff6deb0b068
-	0x7ff6deb0be93
-	0x7ff6df0029a0
-	0x7ff6deffce20
-	0x7ff6df01cc15
-	0x7ff6ded6309e
-	0x7ff6ded6ad8f
-	0x7ff6ded50be4
-	0x7ff6ded50d9f
-	0x7ff6ded367f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>£46.74</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£59.77</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff645307a05
-	0x7ff645307a60
-	0x7ff6450816ad
-	0x7ff6450da13e
-	0x7ff6450da44c
-	0x7ff64512ebe7
-	0x7ff64512b8fb
-	0x7ff6450cb068
-	0x7ff6450cbe93
-	0x7ff6455c29a0
-	0x7ff6455bce20
-	0x7ff6455dcc15
-	0x7ff64532309e
-	0x7ff64532ad8f
-	0x7ff645310be4
-	0x7ff645310d9f
-	0x7ff6452f67f8
+	0x7ff72c327a05
+	0x7ff72c327a60
+	0x7ff72c0a16ad
+	0x7ff72c0fa13e
+	0x7ff72c0fa44c
+	0x7ff72c14ebe7
+	0x7ff72c14b8fb
+	0x7ff72c0eb068
+	0x7ff72c0ebe93
+	0x7ff72c5e29a0
+	0x7ff72c5dce20
+	0x7ff72c5fcc15
+	0x7ff72c34309e
+	0x7ff72c34ad8f
+	0x7ff72c330be4
+	0x7ff72c330d9f
+	0x7ff72c3167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-11-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,26 +589,26 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£11.40</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,26 +709,26 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -751,7 +751,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -829,26 +829,26 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -871,7 +871,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -949,26 +949,26 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -991,7 +991,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1069,26 +1069,26 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1189,26 +1189,26 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1309,26 +1309,26 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1429,26 +1429,26 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1549,26 +1549,26 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1669,26 +1669,26 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1789,26 +1789,26 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1909,26 +1909,26 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£46.74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2029,26 +2029,26 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2149,26 +2149,26 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2269,26 +2269,26 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2486,26 +2486,26 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2606,26 +2606,26 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2726,26 +2726,26 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2846,26 +2846,26 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2966,26 +2966,26 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3086,26 +3086,26 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3206,26 +3206,26 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3326,26 +3326,26 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3446,26 +3446,26 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff72c327a05
-	0x7ff72c327a60
-	0x7ff72c0a16ad
-	0x7ff72c0fa13e
-	0x7ff72c0fa44c
-	0x7ff72c14ebe7
-	0x7ff72c14b8fb
-	0x7ff72c0eb068
-	0x7ff72c0ebe93
-	0x7ff72c5e29a0
-	0x7ff72c5dce20
-	0x7ff72c5fcc15
-	0x7ff72c34309e
-	0x7ff72c34ad8f
-	0x7ff72c330be4
-	0x7ff72c330d9f
-	0x7ff72c3167f8
+	0x7ff7a7427a05
+	0x7ff7a7427a60
+	0x7ff7a71a16ad
+	0x7ff7a71fa13e
+	0x7ff7a71fa44c
+	0x7ff7a724ebe7
+	0x7ff7a724b8fb
+	0x7ff7a71eb068
+	0x7ff7a71ebe93
+	0x7ff7a76e29a0
+	0x7ff7a76dce20
+	0x7ff7a76fcc15
+	0x7ff7a744309e
+	0x7ff7a744ad8f
+	0x7ff7a7430be4
+	0x7ff7a7430d9f
+	0x7ff7a74167f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-11-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,26 +589,26 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£11.40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,26 +709,26 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -751,7 +751,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -829,26 +829,26 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -871,7 +871,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -949,26 +949,26 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -991,7 +991,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1069,26 +1069,26 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1189,26 +1189,26 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1309,26 +1309,26 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1429,26 +1429,26 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1549,26 +1549,26 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1669,26 +1669,26 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1789,26 +1789,26 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1909,26 +1909,26 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2029,26 +2029,26 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2149,26 +2149,26 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2269,26 +2269,26 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2486,26 +2486,26 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2606,26 +2606,26 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2726,26 +2726,26 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2846,26 +2846,26 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2966,26 +2966,26 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3086,26 +3086,26 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3206,26 +3206,26 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3326,26 +3326,26 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3446,26 +3446,26 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7a7427a05
-	0x7ff7a7427a60
-	0x7ff7a71a16ad
-	0x7ff7a71fa13e
-	0x7ff7a71fa44c
-	0x7ff7a724ebe7
-	0x7ff7a724b8fb
-	0x7ff7a71eb068
-	0x7ff7a71ebe93
-	0x7ff7a76e29a0
-	0x7ff7a76dce20
-	0x7ff7a76fcc15
-	0x7ff7a744309e
-	0x7ff7a744ad8f
-	0x7ff7a7430be4
-	0x7ff7a7430d9f
-	0x7ff7a74167f8
+	0x7ff729c57a05
+	0x7ff729c57a60
+	0x7ff7299d16ad
+	0x7ff729a2a13e
+	0x7ff729a2a44c
+	0x7ff729a7ebe7
+	0x7ff729a7b8fb
+	0x7ff729a1b068
+	0x7ff729a1be93
+	0x7ff729f129a0
+	0x7ff729f0ce20
+	0x7ff729f2cc15
+	0x7ff729c7309e
+	0x7ff729c7ad8f
+	0x7ff729c60be4
+	0x7ff729c60d9f
+	0x7ff729c467f8
 	0x7ffef8c5e8d7
 	0x7ffef912c53c
 </t>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
